--- a/diseases/d190/2015-2019.xlsx
+++ b/diseases/d190/2015-2019.xlsx
@@ -769,11 +769,11 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06298651128852252</v>
+        <v>0.06211136964537397</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -917,11 +917,11 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03493783048035233</v>
+        <v>0.03445240035016837</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1065,11 +1065,11 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.09841642388831644</v>
+        <v>0.09704901507089682</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1213,11 +1213,11 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03887448743588499</v>
+        <v>0.03833436095300425</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1361,11 +1361,11 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06839941460237992</v>
+        <v>0.06744906547427329</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1509,11 +1509,11 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07528856427456207</v>
+        <v>0.07424249652923608</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1657,11 +1657,11 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1126868053521223</v>
+        <v>0.1111211222561769</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1805,11 +1805,11 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05658944373578195</v>
+        <v>0.05580318366576568</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1953,11 +1953,11 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.07627272851344524</v>
+        <v>0.07521298667994504</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2101,11 +2101,11 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.06839941460237992</v>
+        <v>0.06744906547427329</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2249,11 +2249,11 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0605261006913146</v>
+        <v>0.05968514426860155</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2397,11 +2397,11 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07824105699121156</v>
+        <v>0.07715396698136298</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2545,11 +2545,11 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.03105179305413164</v>
+        <v>0.03069619448725125</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2693,11 +2693,11 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.05191471651237633</v>
+        <v>0.05132020015837318</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2841,11 +2841,11 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.04318139971590181</v>
+        <v>0.04268689545883377</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2989,11 +2989,11 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.04172584691648939</v>
+        <v>0.04124801134224386</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3137,11 +3137,11 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1906774167230271</v>
+        <v>0.1884938192732772</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3285,11 +3285,11 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.16835894046537</v>
+        <v>0.1664309294855653</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3433,11 +3433,11 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2037773919177389</v>
+        <v>0.2014437763225863</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3581,11 +3581,11 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1678737561988992</v>
+        <v>0.165951301446702</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3729,11 +3729,11 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.170784861797724</v>
+        <v>0.1688290696798818</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3877,11 +3877,11 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1188701452853477</v>
+        <v>0.1175088695215087</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4025,11 +4025,11 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1057701700906359</v>
+        <v>0.1045589124721996</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4173,11 +4173,11 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1047998015576943</v>
+        <v>0.103599656394473</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">

--- a/diseases/d190/2015-2019.xlsx
+++ b/diseases/d190/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4178,6 +4293,11 @@
       <c r="S25" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">

--- a/diseases/d190/2015-2019.xlsx
+++ b/diseases/d190/2015-2019.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.06211136964537397</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.03445240035016837</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.09704901507089682</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0.03833436095300425</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0.06744906547427329</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0.07424249652923608</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0.1111211222561769</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0.05580318366576568</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0.07521298667994504</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0.06744906547427329</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0.05968514426860155</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0.07715396698136298</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0.03069619448725125</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0.05132020015837318</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0.04268689545883377</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0.04124801134224386</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3219,11 +2979,6 @@
       <c r="R18" t="n">
         <v>0.1884938192732772</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3236,22 +2991,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3372,11 +3117,6 @@
       <c r="R19" t="n">
         <v>0.1664309294855653</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3389,22 +3129,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3525,11 +3255,6 @@
       <c r="R20" t="n">
         <v>0.2014437763225863</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3542,22 +3267,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3678,11 +3393,6 @@
       <c r="R21" t="n">
         <v>0.165951301446702</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3405,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3831,11 +3531,6 @@
       <c r="R22" t="n">
         <v>0.1688290696798818</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3848,22 +3543,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3984,11 +3669,6 @@
       <c r="R23" t="n">
         <v>0.1175088695215087</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4001,22 +3681,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4137,11 +3807,6 @@
       <c r="R24" t="n">
         <v>0.1045589124721996</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4154,22 +3819,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4290,11 +3945,6 @@
       <c r="R25" t="n">
         <v>0.103599656394473</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4307,22 +3957,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>

--- a/diseases/d190/2015-2019.xlsx
+++ b/diseases/d190/2015-2019.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0.06211136964537397</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -909,6 +924,11 @@
       <c r="R3" t="n">
         <v>0.03445240035016837</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,12 +941,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1047,6 +1077,11 @@
       <c r="R4" t="n">
         <v>0.09704901507089682</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1059,12 +1094,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1185,6 +1230,11 @@
       <c r="R5" t="n">
         <v>0.03833436095300425</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1197,12 +1247,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1323,6 +1383,11 @@
       <c r="R6" t="n">
         <v>0.06744906547427329</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1335,12 +1400,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1461,6 +1536,11 @@
       <c r="R7" t="n">
         <v>0.07424249652923608</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,12 +1553,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1599,6 +1689,11 @@
       <c r="R8" t="n">
         <v>0.1111211222561769</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1611,12 +1706,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1737,6 +1842,11 @@
       <c r="R9" t="n">
         <v>0.05580318366576568</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1749,12 +1859,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1875,6 +1995,11 @@
       <c r="R10" t="n">
         <v>0.07521298667994504</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1887,12 +2012,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2013,6 +2148,11 @@
       <c r="R11" t="n">
         <v>0.06744906547427329</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2025,12 +2165,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2151,6 +2301,11 @@
       <c r="R12" t="n">
         <v>0.05968514426860155</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2163,12 +2318,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2289,6 +2454,11 @@
       <c r="R13" t="n">
         <v>0.07715396698136298</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,12 +2471,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2427,6 +2607,11 @@
       <c r="R14" t="n">
         <v>0.03069619448725125</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2439,12 +2624,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2565,6 +2760,11 @@
       <c r="R15" t="n">
         <v>0.05132020015837318</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2577,12 +2777,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2703,6 +2913,11 @@
       <c r="R16" t="n">
         <v>0.04268689545883377</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2715,12 +2930,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2841,6 +3066,11 @@
       <c r="R17" t="n">
         <v>0.04124801134224386</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2853,12 +3083,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2979,6 +3219,11 @@
       <c r="R18" t="n">
         <v>0.1884938192732772</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2991,12 +3236,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3117,6 +3372,11 @@
       <c r="R19" t="n">
         <v>0.1664309294855653</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3129,12 +3389,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3255,6 +3525,11 @@
       <c r="R20" t="n">
         <v>0.2014437763225863</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3267,12 +3542,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3393,6 +3678,11 @@
       <c r="R21" t="n">
         <v>0.165951301446702</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3405,12 +3695,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3531,6 +3831,11 @@
       <c r="R22" t="n">
         <v>0.1688290696798818</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3543,12 +3848,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3669,6 +3984,11 @@
       <c r="R23" t="n">
         <v>0.1175088695215087</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3681,12 +4001,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3807,6 +4137,11 @@
       <c r="R24" t="n">
         <v>0.1045589124721996</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3819,12 +4154,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3945,6 +4290,11 @@
       <c r="R25" t="n">
         <v>0.103599656394473</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3957,12 +4307,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
